--- a/PoliVenturiMPUindex.xlsx
+++ b/PoliVenturiMPUindex.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6844"/>
+  <dimension ref="A1:B6880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55182,7 +55182,295 @@
         <v>46106</v>
       </c>
       <c r="B6844" t="n">
-        <v>115.159308472639</v>
+        <v>103.7291041577368</v>
+      </c>
+    </row>
+    <row r="6845">
+      <c r="A6845" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B6845" t="n">
+        <v>119.4456350907273</v>
+      </c>
+    </row>
+    <row r="6846">
+      <c r="A6846" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B6846" t="n">
+        <v>119.4456350907272</v>
+      </c>
+    </row>
+    <row r="6847">
+      <c r="A6847" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B6847" t="n">
+        <v>110.5872267466781</v>
+      </c>
+    </row>
+    <row r="6848">
+      <c r="A6848" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B6848" t="n">
+        <v>112.7303900557223</v>
+      </c>
+    </row>
+    <row r="6849">
+      <c r="A6849" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B6849" t="n">
+        <v>108.1583083297613</v>
+      </c>
+    </row>
+    <row r="6850">
+      <c r="A6850" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B6850" t="n">
+        <v>109.5870838691242</v>
+      </c>
+    </row>
+    <row r="6851">
+      <c r="A6851" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B6851" t="n">
+        <v>109.7299614230605</v>
+      </c>
+    </row>
+    <row r="6852">
+      <c r="A6852" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B6852" t="n">
+        <v>110.1585940848693</v>
+      </c>
+    </row>
+    <row r="6853">
+      <c r="A6853" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B6853" t="n">
+        <v>121.874553507644</v>
+      </c>
+    </row>
+    <row r="6854">
+      <c r="A6854" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B6854" t="n">
+        <v>94.58494070581511</v>
+      </c>
+    </row>
+    <row r="6855">
+      <c r="A6855" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B6855" t="n">
+        <v>100.3000428632662</v>
+      </c>
+    </row>
+    <row r="6856">
+      <c r="A6856" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B6856" t="n">
+        <v>101.8716959565652</v>
+      </c>
+    </row>
+    <row r="6857">
+      <c r="A6857" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B6857" t="n">
+        <v>110.1585940848693</v>
+      </c>
+    </row>
+    <row r="6858">
+      <c r="A6858" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B6858" t="n">
+        <v>99.29989998571216</v>
+      </c>
+    </row>
+    <row r="6859">
+      <c r="A6859" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B6859" t="n">
+        <v>100.4429204172024</v>
+      </c>
+    </row>
+    <row r="6860">
+      <c r="A6860" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B6860" t="n">
+        <v>97.58536933847695</v>
+      </c>
+    </row>
+    <row r="6861">
+      <c r="A6861" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B6861" t="n">
+        <v>93.29904272038867</v>
+      </c>
+    </row>
+    <row r="6862">
+      <c r="A6862" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B6862" t="n">
+        <v>89.01271610230039</v>
+      </c>
+    </row>
+    <row r="6863">
+      <c r="A6863" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B6863" t="n">
+        <v>96.29947135305051</v>
+      </c>
+    </row>
+    <row r="6864">
+      <c r="A6864" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B6864" t="n">
+        <v>100.0142877553935</v>
+      </c>
+    </row>
+    <row r="6865">
+      <c r="A6865" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B6865" t="n">
+        <v>182.0260037148163</v>
+      </c>
+    </row>
+    <row r="6866">
+      <c r="A6866" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B6866" t="n">
+        <v>182.4546363766252</v>
+      </c>
+    </row>
+    <row r="6867">
+      <c r="A6867" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B6867" t="n">
+        <v>190.598656950993</v>
+      </c>
+    </row>
+    <row r="6868">
+      <c r="A6868" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B6868" t="n">
+        <v>203.8862694670667</v>
+      </c>
+    </row>
+    <row r="6869">
+      <c r="A6869" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B6869" t="n">
+        <v>212.3160451493071</v>
+      </c>
+    </row>
+    <row r="6870">
+      <c r="A6870" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B6870" t="n">
+        <v>220.1743106158023</v>
+      </c>
+    </row>
+    <row r="6871">
+      <c r="A6871" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B6871" t="n">
+        <v>220.4600657236748</v>
+      </c>
+    </row>
+    <row r="6872">
+      <c r="A6872" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B6872" t="n">
+        <v>229.4613516216602</v>
+      </c>
+    </row>
+    <row r="6873">
+      <c r="A6873" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B6873" t="n">
+        <v>228.4612087441063</v>
+      </c>
+    </row>
+    <row r="6874">
+      <c r="A6874" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B6874" t="n">
+        <v>198.8855550792971</v>
+      </c>
+    </row>
+    <row r="6875">
+      <c r="A6875" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B6875" t="n">
+        <v>184.4549221317331</v>
+      </c>
+    </row>
+    <row r="6876">
+      <c r="A6876" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B6876" t="n">
+        <v>185.0264323474783</v>
+      </c>
+    </row>
+    <row r="6877">
+      <c r="A6877" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B6877" t="n">
+        <v>195.8851264466352</v>
+      </c>
+    </row>
+    <row r="6878">
+      <c r="A6878" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B6878" t="n">
+        <v>204.029147021003</v>
+      </c>
+    </row>
+    <row r="6879">
+      <c r="A6879" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B6879" t="n">
+        <v>202.8861265895128</v>
+      </c>
+    </row>
+    <row r="6880">
+      <c r="A6880" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B6880" t="n">
+        <v>202.8861265895128</v>
       </c>
     </row>
   </sheetData>
